--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-location.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-location.xlsx
@@ -355,7 +355,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -687,7 +687,7 @@
     <t>場所の実体形態。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
+    <t>http://hl7.org/fhir/ValueSet/location-physical-type|4.0.1</t>
   </si>
   <si>
     <t>.playingEntity [classCode=PLC].code</t>
@@ -916,7 +916,7 @@
     <t>Location.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
